--- a/GT_JUNE_26/30-06-26/Umair.xlsx
+++ b/GT_JUNE_26/30-06-26/Umair.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7814C2-E899-4EE5-B874-7BBF0D5D98EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC081384-D3B4-4B0C-B127-A1E05504E81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -5291,37 +5291,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>8.7584898000000013</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5451,36 +5449,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>8.7584898000000013</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5530,7 +5528,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5551,7 +5549,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5572,7 +5570,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5594,7 +5592,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5619,7 +5617,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5641,7 +5639,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5666,7 +5664,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>8.7584898000000013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5676,7 +5674,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6514,37 +6512,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>80</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>3138.4000000000005</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>109.84400000000002</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>156.92000000000004</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>2871.6360000000004</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>631.75992000000008</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>17.516979600000003</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>3520.9128996000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6674,36 +6670,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>3138.4000000000005</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>109.84400000000002</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>156.92000000000004</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2871.6360000000004</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>631.75992000000008</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>17.516979600000003</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>3520.9128996000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6753,7 +6749,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>3138.4000000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6774,7 +6770,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>156.92000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6795,7 +6791,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>109.84400000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6817,7 +6813,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2871.6360000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6842,7 +6838,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>631.75992000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6864,7 +6860,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>3503.3959200000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6889,7 +6885,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>17.516979600000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6899,7 +6895,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>3520.9128996000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7393,39 +7389,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>20</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>1049.25</v>
-      </c>
-      <c r="J16" s="103">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" s="103"/>
       <c r="K16" s="104">
         <f>I16*$K$13</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>83.94</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>965.31</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>223.90995000000001</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>5.9460997500000001</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>1195.16604975</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -7457,39 +7449,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>20</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>1049.25</v>
-      </c>
-      <c r="J17" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>83.94</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>965.31</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>223.90995000000001</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>5.9460997500000001</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>1195.16604975</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -7577,39 +7565,35 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>20</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>1452.8</v>
-      </c>
-      <c r="J19" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="117"/>
       <c r="K19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>116.224</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>310.02751999999998</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>8.2330176000000002</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7637,39 +7621,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>20</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>1452.8</v>
-      </c>
-      <c r="J20" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>116.224</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>310.02751999999998</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>8.2330176000000002</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7697,39 +7677,35 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>20</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>1452.8</v>
-      </c>
-      <c r="J21" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" s="117"/>
       <c r="K21" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>116.224</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>310.02751999999998</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>8.2330176000000002</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7757,37 +7733,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>8.7584898000000013</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7917,36 +7891,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>8026.1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>595.01200000000006</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>7376.1660000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1693.7824200000002</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>45.3497421</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>9115.2981620999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7996,7 +7970,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>8026.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8017,7 +7991,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>595.01200000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8038,7 +8012,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8060,7 +8034,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>7376.1660000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8085,7 +8059,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1693.7824200000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8107,7 +8081,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>9069.9484200000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8132,7 +8106,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>45.349742100000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8142,7 +8116,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>9115.2981620999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23569,15 +23543,15 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16</f>
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>1836.1875</v>
+        <v>786.9375</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="172">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
@@ -23585,23 +23559,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>146.89499999999998</v>
+        <v>62.954999999999998</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>1689.2925</v>
+        <v>723.98249999999996</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>383.18610000000001</v>
+        <v>159.27615</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>10.362393000000001</v>
+        <v>4.4162932499999998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>2082.8409929999998</v>
+        <v>887.67494324999996</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23643,15 +23617,15 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17</f>
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>1836.1875</v>
+        <v>786.9375</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23659,23 +23633,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>146.89499999999998</v>
+        <v>62.954999999999998</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>1689.2925</v>
+        <v>723.98249999999996</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>394.72784999999999</v>
+        <v>170.81790000000001</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>10.420101750000001</v>
+        <v>4.4740019999999996</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>2094.4404517499997</v>
+        <v>899.27440200000001</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23787,15 +23761,15 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>1452.8</v>
+        <v>0</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="172">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
@@ -23803,23 +23777,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>116.224</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>1336.576</v>
+        <v>0</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>310.02751999999998</v>
+        <v>0</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>8.2330176000000002</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23827,7 +23801,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23857,15 +23831,15 @@
       <c r="G20" s="114"/>
       <c r="H20" s="172">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>1452.8</v>
+        <v>0</v>
       </c>
       <c r="J20" s="172">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23873,23 +23847,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>116.224</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>1336.576</v>
+        <v>0</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>310.02751999999998</v>
+        <v>0</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>8.2330176000000002</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23927,15 +23901,15 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>1452.8</v>
+        <v>0</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="172">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
@@ -23943,23 +23917,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>116.224</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>1336.576</v>
+        <v>0</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>310.02751999999998</v>
+        <v>0</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>8.2330176000000002</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>1654.8365376000002</v>
+        <v>0</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23967,7 +23941,7 @@
       </c>
       <c r="U21" s="164">
         <f>+'8'!P35</f>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23997,11 +23971,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>352</v>
+        <v>152</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>13808.960000000001</v>
+        <v>5962.9600000000009</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -24009,27 +23983,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>483.31360000000018</v>
+        <v>208.70360000000005</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>690.44800000000021</v>
+        <v>298.14800000000008</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>12635.198400000001</v>
+        <v>5456.108400000001</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>2779.7436480000001</v>
+        <v>1200.343848</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>201.44526540000004</v>
+        <v>122.61885720000002</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>15616.3873134</v>
+        <v>6779.0711052000015</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24037,7 +24011,7 @@
       </c>
       <c r="U22" s="164">
         <f>+'9'!P35</f>
-        <v>3520.9128996000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -24107,7 +24081,7 @@
       </c>
       <c r="U23" s="164">
         <f>+'10'!P35</f>
-        <v>9115.2981620999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:21 16384:16384" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
@@ -24187,7 +24161,7 @@
       <c r="B25" s="226"/>
       <c r="C25" s="227">
         <f>H25/40</f>
-        <v>12.05</v>
+        <v>4.55</v>
       </c>
       <c r="D25" s="221"/>
       <c r="E25" s="221"/>
@@ -24198,39 +24172,39 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>482</v>
+        <v>182</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>21839.735000000001</v>
+        <v>7536.8350000000009</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>483.31360000000018</v>
+        <v>208.70360000000005</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>1332.9100000000003</v>
+        <v>424.05800000000011</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>20023.511400000003</v>
+        <v>6904.0734000000011</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>4487.7401580000005</v>
+        <v>1530.4378980000001</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>246.92681295000006</v>
+        <v>131.50915245000002</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>24758.178370950001</v>
+        <v>8566.0204504500016</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24360,7 +24334,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>24758.178370950001</v>
+        <v>8566.0204504500016</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24393,7 +24367,7 @@
       <c r="O32" s="238"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>21839.735000000001</v>
+        <v>7536.8350000000009</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24414,7 +24388,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>1332.9100000000003</v>
+        <v>424.05800000000011</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24435,7 +24409,7 @@
       <c r="O34" s="240"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>483.31360000000018</v>
+        <v>208.70360000000005</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24457,7 +24431,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>20023.511399999999</v>
+        <v>6904.0734000000011</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24482,7 +24456,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>4487.7401580000005</v>
+        <v>1530.4378980000001</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24504,7 +24478,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>24511.251558</v>
+        <v>8434.5112980000013</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24529,7 +24503,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>612.78128894999998</v>
+        <v>210.86278245000005</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24539,7 +24513,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>25124.032846949998</v>
+        <v>8645.3740804500012</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -31495,37 +31469,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31655,36 +31627,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31734,7 +31706,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31755,7 +31727,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31776,7 +31748,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31798,7 +31770,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31823,7 +31795,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31845,7 +31817,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31870,7 +31842,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31880,7 +31852,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
